--- a/sample_data/quarters_invalid.xlsx
+++ b/sample_data/quarters_invalid.xlsx
@@ -17,7 +17,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="165" formatCode="DD-MM-YYYY"/>
+    <numFmt numFmtId="166" formatCode="HH:MM"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -50,9 +54,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -418,17 +424,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,7 +478,22 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>EMD Amount (Rs.)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Bidding Date</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Start Time</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Duration (min)</t>
         </is>
       </c>
     </row>
@@ -503,12 +527,19 @@
         <v>750</v>
       </c>
       <c r="G2" t="n">
-        <v>4500</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Vacant</t>
-        </is>
+        <v>45000</v>
+      </c>
+      <c r="H2" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -541,12 +572,19 @@
         <v>750</v>
       </c>
       <c r="G3" t="n">
-        <v>4600</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Vacant</t>
-        </is>
+        <v>46000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.4201388888888889</v>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -581,12 +619,19 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>3600</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Vacant</t>
-        </is>
+        <v>36000</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.4236111111111111</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -619,12 +664,19 @@
         <v>480</v>
       </c>
       <c r="G5" t="n">
-        <v>-2400</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Vacant</t>
-        </is>
+        <v>-24000</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.4305555555555556</v>
+      </c>
+      <c r="K5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -652,12 +704,205 @@
         <v>980</v>
       </c>
       <c r="G6" t="n">
-        <v>6200</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Vacant</t>
-        </is>
+        <v>62000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="K6" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A-134</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Sector 12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Main road side</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Type A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>980</v>
+      </c>
+      <c r="G7" t="n">
+        <v>60000</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>C-112</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Sector 2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Opposite park</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>620</v>
+      </c>
+      <c r="G8" t="n">
+        <v>39000</v>
+      </c>
+      <c r="H8" t="n">
+        <v>7500</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>31-02-2026</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>D-203</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sector 9</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Near school</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Type D</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2nd</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>480</v>
+      </c>
+      <c r="G9" t="n">
+        <v>27000</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5500</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>46308</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>B-118</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Sector 4</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Near market</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Type B</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ground</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>750</v>
+      </c>
+      <c r="G10" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9500</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>25:00</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -684,7 +929,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deliberate errors: duplicate Quarter No (row 3), non-numeric Area (row 4), negative Base Rate (row 5), missing Quarter No (row 6).</t>
+          <t>Deliberate errors: duplicate Quarter No (row 3), non-numeric Area (row 4), negative Base Rate (row 5), missing Quarter No (row 6), EMD 0 (row 7), impossible date (row 8), start in the past (row 9), bad time and zero duration (row 10).</t>
         </is>
       </c>
     </row>
